--- a/Excel_files/susswein_2025_model.xlsx
+++ b/Excel_files/susswein_2025_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB48E6E-8C16-427E-9ABE-CFA3B570228A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F1566A-8A1D-42C6-91B0-B20D59A6200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" activeTab="5" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
@@ -3464,7 +3464,7 @@
     <col min="304" max="16384" width="9.1796875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:141" x14ac:dyDescent="0.35">
       <c r="D1" s="55" t="s">
         <v>86</v>
       </c>
@@ -3618,7 +3618,7 @@
       <c r="EJ1" s="154"/>
       <c r="EK1" s="155"/>
     </row>
-    <row r="2" spans="1:246" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:141" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E2" s="158" t="s">
         <v>88</v>
       </c>
@@ -3789,7 +3789,7 @@
       <c r="EJ2" s="150"/>
       <c r="EK2" s="152"/>
     </row>
-    <row r="3" spans="1:246" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:141" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="90" t="s">
         <v>0</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A4" s="89" t="s">
         <v>166</v>
       </c>
@@ -4448,7 +4448,7 @@
       <c r="EJ4" s="146"/>
       <c r="EK4" s="148"/>
     </row>
-    <row r="5" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A5" s="89" t="s">
         <v>167</v>
       </c>
@@ -4685,7 +4685,7 @@
       <c r="EJ5" s="17"/>
       <c r="EK5" s="19"/>
     </row>
-    <row r="6" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A6" s="89" t="s">
         <v>168</v>
       </c>
@@ -4956,63 +4956,25 @@
       <c r="DH6" s="17"/>
       <c r="DI6" s="17"/>
       <c r="DJ6" s="19"/>
-      <c r="DK6" s="43">
-        <v>200</v>
-      </c>
-      <c r="DL6" s="17">
-        <v>1</v>
-      </c>
-      <c r="DM6" s="17">
-        <v>-35</v>
-      </c>
-      <c r="DN6" s="17">
-        <v>0</v>
-      </c>
-      <c r="DO6" s="17">
-        <v>-20</v>
-      </c>
-      <c r="DP6" s="17">
-        <v>2</v>
-      </c>
-      <c r="DQ6" s="17">
-        <v>1</v>
-      </c>
-      <c r="DR6" s="17">
-        <v>1.4E-2</v>
-      </c>
-      <c r="DS6" s="17">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="DT6" s="17">
-        <v>20</v>
-      </c>
-      <c r="DU6" s="17">
-        <v>7</v>
-      </c>
-      <c r="DV6" s="17">
-        <v>1</v>
-      </c>
-      <c r="DW6" s="17">
-        <v>-15</v>
-      </c>
-      <c r="DX6" s="17">
-        <v>-6</v>
-      </c>
-      <c r="DY6" s="17">
-        <v>1</v>
-      </c>
-      <c r="DZ6" s="17">
-        <v>0</v>
-      </c>
-      <c r="EA6" s="17">
-        <v>1000</v>
-      </c>
-      <c r="EB6" s="17">
-        <v>7</v>
-      </c>
-      <c r="EC6" s="17">
-        <v>1</v>
-      </c>
+      <c r="DK6" s="43"/>
+      <c r="DL6" s="17"/>
+      <c r="DM6" s="17"/>
+      <c r="DN6" s="17"/>
+      <c r="DO6" s="17"/>
+      <c r="DP6" s="17"/>
+      <c r="DQ6" s="17"/>
+      <c r="DR6" s="17"/>
+      <c r="DS6" s="17"/>
+      <c r="DT6" s="17"/>
+      <c r="DU6" s="17"/>
+      <c r="DV6" s="17"/>
+      <c r="DW6" s="17"/>
+      <c r="DX6" s="17"/>
+      <c r="DY6" s="17"/>
+      <c r="DZ6" s="17"/>
+      <c r="EA6" s="17"/>
+      <c r="EB6" s="17"/>
+      <c r="EC6" s="17"/>
       <c r="ED6" s="17"/>
       <c r="EE6" s="17"/>
       <c r="EF6" s="17"/>
@@ -5022,7 +4984,7 @@
       <c r="EJ6" s="17"/>
       <c r="EK6" s="19"/>
     </row>
-    <row r="7" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A7" s="89" t="s">
         <v>169</v>
       </c>
@@ -5273,107 +5235,83 @@
       <c r="DH7" s="17"/>
       <c r="DI7" s="17"/>
       <c r="DJ7" s="19"/>
-      <c r="DK7" s="43"/>
-      <c r="DL7" s="17"/>
-      <c r="DM7" s="17"/>
-      <c r="DN7" s="17"/>
-      <c r="DO7" s="17"/>
-      <c r="DP7" s="17"/>
-      <c r="DQ7" s="17"/>
-      <c r="DR7" s="17"/>
-      <c r="DS7" s="17"/>
-      <c r="DT7" s="17"/>
-      <c r="DU7" s="17"/>
-      <c r="DV7" s="17"/>
-      <c r="DW7" s="17"/>
-      <c r="DX7" s="17"/>
-      <c r="DY7" s="17"/>
-      <c r="DZ7" s="17"/>
-      <c r="EA7" s="17"/>
-      <c r="EB7" s="17"/>
-      <c r="EC7" s="17"/>
-      <c r="ED7" s="17"/>
-      <c r="EE7" s="17"/>
-      <c r="EF7" s="17"/>
-      <c r="EG7" s="17"/>
-      <c r="EH7" s="17"/>
+      <c r="DK7" s="43">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="DL7" s="17">
+        <v>3</v>
+      </c>
+      <c r="DM7" s="17">
+        <v>50</v>
+      </c>
+      <c r="DN7" s="17">
+        <v>0</v>
+      </c>
+      <c r="DO7" s="17">
+        <v>-48</v>
+      </c>
+      <c r="DP7" s="17">
+        <v>4</v>
+      </c>
+      <c r="DQ7" s="17">
+        <v>2</v>
+      </c>
+      <c r="DR7" s="17">
+        <v>0.16</v>
+      </c>
+      <c r="DS7" s="17">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="DT7" s="17">
+        <v>-30</v>
+      </c>
+      <c r="DU7" s="17">
+        <v>4</v>
+      </c>
+      <c r="DV7" s="17">
+        <v>4</v>
+      </c>
+      <c r="DW7" s="17">
+        <v>-50</v>
+      </c>
+      <c r="DX7" s="17">
+        <v>-4</v>
+      </c>
+      <c r="DY7" s="17">
+        <v>4</v>
+      </c>
+      <c r="DZ7" s="17">
+        <v>0</v>
+      </c>
+      <c r="EA7" s="17">
+        <v>-57</v>
+      </c>
+      <c r="EB7" s="17">
+        <v>5</v>
+      </c>
+      <c r="EC7" s="17">
+        <v>2</v>
+      </c>
+      <c r="ED7" s="17">
+        <v>2</v>
+      </c>
+      <c r="EE7" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="EF7" s="17">
+        <v>-44</v>
+      </c>
+      <c r="EG7" s="17">
+        <v>-3</v>
+      </c>
+      <c r="EH7" s="17">
+        <v>4</v>
+      </c>
       <c r="EI7" s="17"/>
       <c r="EJ7" s="17"/>
       <c r="EK7" s="19"/>
-      <c r="HO7" s="14">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="HP7" s="14">
-        <v>3</v>
-      </c>
-      <c r="HQ7" s="14">
-        <v>50</v>
-      </c>
-      <c r="HR7" s="14">
-        <v>0</v>
-      </c>
-      <c r="HS7" s="14">
-        <v>-48</v>
-      </c>
-      <c r="HT7" s="14">
-        <v>4</v>
-      </c>
-      <c r="HU7" s="14">
-        <v>2</v>
-      </c>
-      <c r="HV7" s="14">
-        <v>0.16</v>
-      </c>
-      <c r="HW7" s="14">
-        <v>1.4999999999999999E-4</v>
-      </c>
-      <c r="HX7" s="14">
-        <v>-30</v>
-      </c>
-      <c r="HY7" s="14">
-        <v>4</v>
-      </c>
-      <c r="HZ7" s="14">
-        <v>4</v>
-      </c>
-      <c r="IA7" s="14">
-        <v>-50</v>
-      </c>
-      <c r="IB7" s="14">
-        <v>-4</v>
-      </c>
-      <c r="IC7" s="14">
-        <v>4</v>
-      </c>
-      <c r="ID7" s="14">
-        <v>0</v>
-      </c>
-      <c r="IE7" s="14">
-        <v>-57</v>
-      </c>
-      <c r="IF7" s="14">
-        <v>5</v>
-      </c>
-      <c r="IG7" s="14">
-        <v>2</v>
-      </c>
-      <c r="IH7" s="14">
-        <v>2</v>
-      </c>
-      <c r="II7" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="IJ7" s="14">
-        <v>-44</v>
-      </c>
-      <c r="IK7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="IL7" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:246" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A8" s="89" t="s">
         <v>170</v>
       </c>
@@ -5582,107 +5520,83 @@
       <c r="DH8" s="17"/>
       <c r="DI8" s="17"/>
       <c r="DJ8" s="19"/>
-      <c r="DK8" s="43"/>
-      <c r="DL8" s="17"/>
-      <c r="DM8" s="17"/>
-      <c r="DN8" s="17"/>
-      <c r="DO8" s="17"/>
-      <c r="DP8" s="17"/>
-      <c r="DQ8" s="17"/>
-      <c r="DR8" s="17"/>
-      <c r="DS8" s="17"/>
-      <c r="DT8" s="17"/>
-      <c r="DU8" s="17"/>
-      <c r="DV8" s="17"/>
-      <c r="DW8" s="17"/>
-      <c r="DX8" s="17"/>
-      <c r="DY8" s="17"/>
-      <c r="DZ8" s="17"/>
-      <c r="EA8" s="17"/>
-      <c r="EB8" s="17"/>
-      <c r="EC8" s="17"/>
-      <c r="ED8" s="17"/>
-      <c r="EE8" s="17"/>
-      <c r="EF8" s="17"/>
-      <c r="EG8" s="17"/>
-      <c r="EH8" s="17"/>
+      <c r="DK8" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="DL8" s="17">
+        <v>3</v>
+      </c>
+      <c r="DM8" s="17">
+        <v>50</v>
+      </c>
+      <c r="DN8" s="17">
+        <v>0</v>
+      </c>
+      <c r="DO8" s="17">
+        <v>-48</v>
+      </c>
+      <c r="DP8" s="17">
+        <v>4</v>
+      </c>
+      <c r="DQ8" s="17">
+        <v>2</v>
+      </c>
+      <c r="DR8" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="DS8" s="17">
+        <v>0.04</v>
+      </c>
+      <c r="DT8" s="17">
+        <v>-56</v>
+      </c>
+      <c r="DU8" s="17">
+        <v>-3</v>
+      </c>
+      <c r="DV8" s="17">
+        <v>4</v>
+      </c>
+      <c r="DW8" s="17">
+        <v>-30</v>
+      </c>
+      <c r="DX8" s="17">
+        <v>-3</v>
+      </c>
+      <c r="DY8" s="17">
+        <v>4</v>
+      </c>
+      <c r="DZ8" s="17">
+        <v>0</v>
+      </c>
+      <c r="EA8" s="17">
+        <v>-56</v>
+      </c>
+      <c r="EB8" s="17">
+        <v>5</v>
+      </c>
+      <c r="EC8" s="17">
+        <v>2</v>
+      </c>
+      <c r="ED8" s="17">
+        <v>3</v>
+      </c>
+      <c r="EE8" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="EF8" s="17">
+        <v>-40</v>
+      </c>
+      <c r="EG8" s="17">
+        <v>-2</v>
+      </c>
+      <c r="EH8" s="17">
+        <v>4</v>
+      </c>
       <c r="EI8" s="17"/>
       <c r="EJ8" s="17"/>
       <c r="EK8" s="19"/>
-      <c r="HO8" s="14">
-        <v>0.01</v>
-      </c>
-      <c r="HP8" s="14">
-        <v>3</v>
-      </c>
-      <c r="HQ8" s="14">
-        <v>50</v>
-      </c>
-      <c r="HR8" s="14">
-        <v>0</v>
-      </c>
-      <c r="HS8" s="14">
-        <v>-48</v>
-      </c>
-      <c r="HT8" s="14">
-        <v>4</v>
-      </c>
-      <c r="HU8" s="14">
-        <v>2</v>
-      </c>
-      <c r="HV8" s="14">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="HW8" s="14">
-        <v>0.04</v>
-      </c>
-      <c r="HX8" s="14">
-        <v>-56</v>
-      </c>
-      <c r="HY8" s="14">
-        <v>-3</v>
-      </c>
-      <c r="HZ8" s="14">
-        <v>4</v>
-      </c>
-      <c r="IA8" s="14">
-        <v>-30</v>
-      </c>
-      <c r="IB8" s="14">
-        <v>-3</v>
-      </c>
-      <c r="IC8" s="14">
-        <v>4</v>
-      </c>
-      <c r="ID8" s="14">
-        <v>0</v>
-      </c>
-      <c r="IE8" s="14">
-        <v>-56</v>
-      </c>
-      <c r="IF8" s="14">
-        <v>5</v>
-      </c>
-      <c r="IG8" s="14">
-        <v>2</v>
-      </c>
-      <c r="IH8" s="14">
-        <v>3</v>
-      </c>
-      <c r="II8" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="IJ8" s="14">
-        <v>-40</v>
-      </c>
-      <c r="IK8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="IL8" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:246" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A9" s="89" t="s">
         <v>171</v>
       </c>
@@ -5919,7 +5833,7 @@
       <c r="EJ9" s="17"/>
       <c r="EK9" s="19"/>
     </row>
-    <row r="10" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A10" s="89" t="s">
         <v>172</v>
       </c>
@@ -6156,7 +6070,7 @@
       <c r="EJ10" s="17"/>
       <c r="EK10" s="19"/>
     </row>
-    <row r="11" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A11" s="89" t="s">
         <v>173</v>
       </c>
@@ -6443,63 +6357,25 @@
       <c r="DH11" s="17"/>
       <c r="DI11" s="17"/>
       <c r="DJ11" s="19"/>
-      <c r="DK11" s="43">
-        <v>200</v>
-      </c>
-      <c r="DL11" s="17">
-        <v>1</v>
-      </c>
-      <c r="DM11" s="17">
-        <v>-35</v>
-      </c>
-      <c r="DN11" s="17">
-        <v>0</v>
-      </c>
-      <c r="DO11" s="17">
-        <v>-20</v>
-      </c>
-      <c r="DP11" s="17">
-        <v>2</v>
-      </c>
-      <c r="DQ11" s="17">
-        <v>1</v>
-      </c>
-      <c r="DR11" s="17">
-        <v>1.4E-2</v>
-      </c>
-      <c r="DS11" s="17">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="DT11" s="17">
-        <v>20</v>
-      </c>
-      <c r="DU11" s="17">
-        <v>7</v>
-      </c>
-      <c r="DV11" s="17">
-        <v>1</v>
-      </c>
-      <c r="DW11" s="17">
-        <v>-15</v>
-      </c>
-      <c r="DX11" s="17">
-        <v>-6</v>
-      </c>
-      <c r="DY11" s="17">
-        <v>1</v>
-      </c>
-      <c r="DZ11" s="17">
-        <v>0</v>
-      </c>
-      <c r="EA11" s="17">
-        <v>1000</v>
-      </c>
-      <c r="EB11" s="17">
-        <v>7</v>
-      </c>
-      <c r="EC11" s="17">
-        <v>1</v>
-      </c>
+      <c r="DK11" s="43"/>
+      <c r="DL11" s="17"/>
+      <c r="DM11" s="17"/>
+      <c r="DN11" s="17"/>
+      <c r="DO11" s="17"/>
+      <c r="DP11" s="17"/>
+      <c r="DQ11" s="17"/>
+      <c r="DR11" s="17"/>
+      <c r="DS11" s="17"/>
+      <c r="DT11" s="17"/>
+      <c r="DU11" s="17"/>
+      <c r="DV11" s="17"/>
+      <c r="DW11" s="17"/>
+      <c r="DX11" s="17"/>
+      <c r="DY11" s="17"/>
+      <c r="DZ11" s="17"/>
+      <c r="EA11" s="17"/>
+      <c r="EB11" s="17"/>
+      <c r="EC11" s="17"/>
       <c r="ED11" s="17"/>
       <c r="EE11" s="17"/>
       <c r="EF11" s="17"/>
@@ -6509,7 +6385,7 @@
       <c r="EJ11" s="17"/>
       <c r="EK11" s="19"/>
     </row>
-    <row r="12" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A12" s="89" t="s">
         <v>174</v>
       </c>
@@ -6760,107 +6636,83 @@
       <c r="DH12" s="17"/>
       <c r="DI12" s="17"/>
       <c r="DJ12" s="19"/>
-      <c r="DK12" s="43"/>
-      <c r="DL12" s="17"/>
-      <c r="DM12" s="17"/>
-      <c r="DN12" s="17"/>
-      <c r="DO12" s="17"/>
-      <c r="DP12" s="17"/>
-      <c r="DQ12" s="17"/>
-      <c r="DR12" s="17"/>
-      <c r="DS12" s="17"/>
-      <c r="DT12" s="17"/>
-      <c r="DU12" s="17"/>
-      <c r="DV12" s="17"/>
-      <c r="DW12" s="17"/>
-      <c r="DX12" s="17"/>
-      <c r="DY12" s="17"/>
-      <c r="DZ12" s="17"/>
-      <c r="EA12" s="17"/>
-      <c r="EB12" s="17"/>
-      <c r="EC12" s="17"/>
-      <c r="ED12" s="17"/>
-      <c r="EE12" s="17"/>
-      <c r="EF12" s="17"/>
-      <c r="EG12" s="17"/>
-      <c r="EH12" s="17"/>
+      <c r="DK12" s="43">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="DL12" s="17">
+        <v>3</v>
+      </c>
+      <c r="DM12" s="17">
+        <v>50</v>
+      </c>
+      <c r="DN12" s="17">
+        <v>0</v>
+      </c>
+      <c r="DO12" s="17">
+        <v>-48</v>
+      </c>
+      <c r="DP12" s="17">
+        <v>4</v>
+      </c>
+      <c r="DQ12" s="17">
+        <v>2</v>
+      </c>
+      <c r="DR12" s="17">
+        <v>0.16</v>
+      </c>
+      <c r="DS12" s="17">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="DT12" s="17">
+        <v>-30</v>
+      </c>
+      <c r="DU12" s="17">
+        <v>4</v>
+      </c>
+      <c r="DV12" s="17">
+        <v>4</v>
+      </c>
+      <c r="DW12" s="17">
+        <v>-50</v>
+      </c>
+      <c r="DX12" s="17">
+        <v>-4</v>
+      </c>
+      <c r="DY12" s="17">
+        <v>4</v>
+      </c>
+      <c r="DZ12" s="17">
+        <v>0</v>
+      </c>
+      <c r="EA12" s="17">
+        <v>-57</v>
+      </c>
+      <c r="EB12" s="17">
+        <v>5</v>
+      </c>
+      <c r="EC12" s="17">
+        <v>2</v>
+      </c>
+      <c r="ED12" s="17">
+        <v>2</v>
+      </c>
+      <c r="EE12" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="EF12" s="17">
+        <v>-44</v>
+      </c>
+      <c r="EG12" s="17">
+        <v>-3</v>
+      </c>
+      <c r="EH12" s="17">
+        <v>4</v>
+      </c>
       <c r="EI12" s="17"/>
       <c r="EJ12" s="17"/>
       <c r="EK12" s="19"/>
-      <c r="HO12" s="14">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="HP12" s="14">
-        <v>3</v>
-      </c>
-      <c r="HQ12" s="14">
-        <v>50</v>
-      </c>
-      <c r="HR12" s="14">
-        <v>0</v>
-      </c>
-      <c r="HS12" s="14">
-        <v>-48</v>
-      </c>
-      <c r="HT12" s="14">
-        <v>4</v>
-      </c>
-      <c r="HU12" s="14">
-        <v>2</v>
-      </c>
-      <c r="HV12" s="14">
-        <v>0.16</v>
-      </c>
-      <c r="HW12" s="14">
-        <v>1.4999999999999999E-4</v>
-      </c>
-      <c r="HX12" s="14">
-        <v>-30</v>
-      </c>
-      <c r="HY12" s="14">
-        <v>4</v>
-      </c>
-      <c r="HZ12" s="14">
-        <v>4</v>
-      </c>
-      <c r="IA12" s="14">
-        <v>-50</v>
-      </c>
-      <c r="IB12" s="14">
-        <v>-4</v>
-      </c>
-      <c r="IC12" s="14">
-        <v>4</v>
-      </c>
-      <c r="ID12" s="14">
-        <v>0</v>
-      </c>
-      <c r="IE12" s="14">
-        <v>-57</v>
-      </c>
-      <c r="IF12" s="14">
-        <v>5</v>
-      </c>
-      <c r="IG12" s="14">
-        <v>2</v>
-      </c>
-      <c r="IH12" s="14">
-        <v>2</v>
-      </c>
-      <c r="II12" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="IJ12" s="14">
-        <v>-44</v>
-      </c>
-      <c r="IK12" s="14">
-        <v>-3</v>
-      </c>
-      <c r="IL12" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:246" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A13" s="89" t="s">
         <v>175</v>
       </c>
@@ -7069,107 +6921,83 @@
       <c r="DH13" s="17"/>
       <c r="DI13" s="17"/>
       <c r="DJ13" s="19"/>
-      <c r="DK13" s="43"/>
-      <c r="DL13" s="17"/>
-      <c r="DM13" s="17"/>
-      <c r="DN13" s="17"/>
-      <c r="DO13" s="17"/>
-      <c r="DP13" s="17"/>
-      <c r="DQ13" s="17"/>
-      <c r="DR13" s="17"/>
-      <c r="DS13" s="17"/>
-      <c r="DT13" s="17"/>
-      <c r="DU13" s="17"/>
-      <c r="DV13" s="17"/>
-      <c r="DW13" s="17"/>
-      <c r="DX13" s="17"/>
-      <c r="DY13" s="17"/>
-      <c r="DZ13" s="17"/>
-      <c r="EA13" s="17"/>
-      <c r="EB13" s="17"/>
-      <c r="EC13" s="17"/>
-      <c r="ED13" s="17"/>
-      <c r="EE13" s="17"/>
-      <c r="EF13" s="17"/>
-      <c r="EG13" s="17"/>
-      <c r="EH13" s="17"/>
+      <c r="DK13" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="DL13" s="17">
+        <v>3</v>
+      </c>
+      <c r="DM13" s="17">
+        <v>50</v>
+      </c>
+      <c r="DN13" s="17">
+        <v>0</v>
+      </c>
+      <c r="DO13" s="17">
+        <v>-48</v>
+      </c>
+      <c r="DP13" s="17">
+        <v>4</v>
+      </c>
+      <c r="DQ13" s="17">
+        <v>2</v>
+      </c>
+      <c r="DR13" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="DS13" s="17">
+        <v>0.04</v>
+      </c>
+      <c r="DT13" s="17">
+        <v>-56</v>
+      </c>
+      <c r="DU13" s="17">
+        <v>-3</v>
+      </c>
+      <c r="DV13" s="17">
+        <v>4</v>
+      </c>
+      <c r="DW13" s="17">
+        <v>-30</v>
+      </c>
+      <c r="DX13" s="17">
+        <v>-3</v>
+      </c>
+      <c r="DY13" s="17">
+        <v>4</v>
+      </c>
+      <c r="DZ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="EA13" s="17">
+        <v>-56</v>
+      </c>
+      <c r="EB13" s="17">
+        <v>5</v>
+      </c>
+      <c r="EC13" s="17">
+        <v>2</v>
+      </c>
+      <c r="ED13" s="17">
+        <v>3</v>
+      </c>
+      <c r="EE13" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="EF13" s="17">
+        <v>-40</v>
+      </c>
+      <c r="EG13" s="17">
+        <v>-2</v>
+      </c>
+      <c r="EH13" s="17">
+        <v>4</v>
+      </c>
       <c r="EI13" s="17"/>
       <c r="EJ13" s="17"/>
       <c r="EK13" s="19"/>
-      <c r="HO13" s="14">
-        <v>0.01</v>
-      </c>
-      <c r="HP13" s="14">
-        <v>3</v>
-      </c>
-      <c r="HQ13" s="14">
-        <v>50</v>
-      </c>
-      <c r="HR13" s="14">
-        <v>0</v>
-      </c>
-      <c r="HS13" s="14">
-        <v>-48</v>
-      </c>
-      <c r="HT13" s="14">
-        <v>4</v>
-      </c>
-      <c r="HU13" s="14">
-        <v>2</v>
-      </c>
-      <c r="HV13" s="14">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="HW13" s="14">
-        <v>0.04</v>
-      </c>
-      <c r="HX13" s="14">
-        <v>-56</v>
-      </c>
-      <c r="HY13" s="14">
-        <v>-3</v>
-      </c>
-      <c r="HZ13" s="14">
-        <v>4</v>
-      </c>
-      <c r="IA13" s="14">
-        <v>-30</v>
-      </c>
-      <c r="IB13" s="14">
-        <v>-3</v>
-      </c>
-      <c r="IC13" s="14">
-        <v>4</v>
-      </c>
-      <c r="ID13" s="14">
-        <v>0</v>
-      </c>
-      <c r="IE13" s="14">
-        <v>-56</v>
-      </c>
-      <c r="IF13" s="14">
-        <v>5</v>
-      </c>
-      <c r="IG13" s="14">
-        <v>2</v>
-      </c>
-      <c r="IH13" s="14">
-        <v>3</v>
-      </c>
-      <c r="II13" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="IJ13" s="14">
-        <v>-40</v>
-      </c>
-      <c r="IK13" s="14">
-        <v>-2</v>
-      </c>
-      <c r="IL13" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:246" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A14" s="89">
         <f>Neu!B14</f>
         <v>0</v>
@@ -7315,7 +7143,7 @@
       <c r="EJ14" s="17"/>
       <c r="EK14" s="19"/>
     </row>
-    <row r="15" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A15" s="89">
         <f>Neu!B15</f>
         <v>0</v>
@@ -7461,7 +7289,7 @@
       <c r="EJ15" s="17"/>
       <c r="EK15" s="19"/>
     </row>
-    <row r="16" spans="1:246" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:141" x14ac:dyDescent="0.35">
       <c r="A16" s="89">
         <f>Neu!B16</f>
         <v>0</v>
@@ -8856,49 +8684,6 @@
       <c r="EF25" s="23"/>
       <c r="EG25" s="23"/>
       <c r="EH25" s="23"/>
-      <c r="FE25" s="23"/>
-      <c r="FF25" s="23"/>
-      <c r="FG25" s="23"/>
-      <c r="FH25" s="23"/>
-      <c r="FI25" s="23"/>
-      <c r="FL25" s="23"/>
-      <c r="GL25" s="23"/>
-      <c r="HM25" s="23"/>
-      <c r="HO25" s="23"/>
-      <c r="HP25" s="23"/>
-      <c r="HQ25" s="23"/>
-      <c r="HR25" s="23"/>
-      <c r="HS25" s="23"/>
-      <c r="HT25" s="23"/>
-      <c r="HU25" s="23"/>
-      <c r="HV25" s="23"/>
-      <c r="HW25" s="23"/>
-      <c r="HX25" s="23"/>
-      <c r="HY25" s="23"/>
-      <c r="HZ25" s="23"/>
-      <c r="IA25" s="23"/>
-      <c r="IB25" s="23"/>
-      <c r="IC25" s="23"/>
-      <c r="ID25" s="23"/>
-      <c r="IE25" s="23"/>
-      <c r="IF25" s="23"/>
-      <c r="IG25" s="23"/>
-      <c r="IH25" s="23"/>
-      <c r="IP25" s="23"/>
-      <c r="IQ25" s="23"/>
-      <c r="IR25" s="23"/>
-      <c r="IS25" s="23"/>
-      <c r="IT25" s="23"/>
-      <c r="IU25" s="23"/>
-      <c r="IV25" s="23"/>
-      <c r="IW25" s="23"/>
-      <c r="IX25" s="23"/>
-      <c r="IY25" s="23"/>
-      <c r="IZ25" s="23"/>
-      <c r="JA25" s="23"/>
-      <c r="JB25" s="23"/>
-      <c r="JC25" s="23"/>
-      <c r="JD25" s="23"/>
     </row>
     <row r="26" spans="1:264" x14ac:dyDescent="0.35">
       <c r="G26" s="23"/>
@@ -10982,29 +10767,24 @@
       <formula>LEN(TRIM(FE26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FE25:FI25">
-    <cfRule type="notContainsBlanks" dxfId="31" priority="53">
-      <formula>LEN(TRIM(FE25))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="FE27:FI27">
     <cfRule type="notContainsBlanks" dxfId="30" priority="51">
       <formula>LEN(TRIM(FE27))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FL25:FL27">
+  <conditionalFormatting sqref="FL26:FL27">
     <cfRule type="notContainsBlanks" dxfId="29" priority="44">
-      <formula>LEN(TRIM(FL25))&gt;0</formula>
+      <formula>LEN(TRIM(FL26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="GL25:GL27">
+  <conditionalFormatting sqref="GL26:GL27">
     <cfRule type="notContainsBlanks" dxfId="28" priority="75">
-      <formula>LEN(TRIM(GL25))&gt;0</formula>
+      <formula>LEN(TRIM(GL26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="HM25:HM27">
+  <conditionalFormatting sqref="HM26:HM27">
     <cfRule type="notContainsBlanks" dxfId="27" priority="37">
-      <formula>LEN(TRIM(HM25))&gt;0</formula>
+      <formula>LEN(TRIM(HM26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HO29:HO31">
@@ -11012,29 +10792,24 @@
       <formula>LEN(TRIM(HO29))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="HO25:HU25 ID25:IH25">
-    <cfRule type="notContainsBlanks" dxfId="25" priority="147">
-      <formula>LEN(TRIM(HO25))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="HO27:HU27 ID27:IH27">
     <cfRule type="notContainsBlanks" dxfId="24" priority="139">
       <formula>LEN(TRIM(HO27))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="HV25:IC27">
+  <conditionalFormatting sqref="HV26:IC27">
     <cfRule type="notContainsBlanks" dxfId="23" priority="24">
-      <formula>LEN(TRIM(HV25))&gt;0</formula>
+      <formula>LEN(TRIM(HV26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="IP25:IV26">
+  <conditionalFormatting sqref="IP26:IV26">
     <cfRule type="notContainsBlanks" dxfId="22" priority="95">
-      <formula>LEN(TRIM(IP25))&gt;0</formula>
+      <formula>LEN(TRIM(IP26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="IW25:JD27">
+  <conditionalFormatting sqref="IW26:JD27">
     <cfRule type="notContainsBlanks" dxfId="21" priority="101">
-      <formula>LEN(TRIM(IW25))&gt;0</formula>
+      <formula>LEN(TRIM(IW26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel_files/susswein_2025_model.xlsx
+++ b/Excel_files/susswein_2025_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F1566A-8A1D-42C6-91B0-B20D59A6200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5E7A68-A482-427C-A666-B4ECB554A5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" activeTab="2" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="193">
   <si>
     <t>Name</t>
   </si>
@@ -2125,18 +2125,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2146,19 +2134,37 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2167,22 +2173,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2190,6 +2187,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2213,7 +2213,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="45">
     <dxf>
       <font>
         <strike val="0"/>
@@ -2373,26 +2373,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3468,326 +3448,326 @@
       <c r="D1" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="156" t="s">
+      <c r="E1" s="157" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="157"/>
-      <c r="G1" s="153" t="s">
+      <c r="F1" s="158"/>
+      <c r="G1" s="149" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="154"/>
-      <c r="AA1" s="154"/>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="154"/>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="155"/>
-      <c r="AH1" s="153" t="s">
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+      <c r="V1" s="150"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
+      <c r="Y1" s="150"/>
+      <c r="Z1" s="150"/>
+      <c r="AA1" s="150"/>
+      <c r="AB1" s="150"/>
+      <c r="AC1" s="150"/>
+      <c r="AD1" s="150"/>
+      <c r="AE1" s="150"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="151"/>
+      <c r="AH1" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="AI1" s="154"/>
-      <c r="AJ1" s="154"/>
-      <c r="AK1" s="154"/>
-      <c r="AL1" s="154"/>
-      <c r="AM1" s="154"/>
-      <c r="AN1" s="154"/>
-      <c r="AO1" s="154"/>
-      <c r="AP1" s="154"/>
-      <c r="AQ1" s="154"/>
-      <c r="AR1" s="154"/>
-      <c r="AS1" s="154"/>
-      <c r="AT1" s="154"/>
-      <c r="AU1" s="154"/>
-      <c r="AV1" s="154"/>
-      <c r="AW1" s="154"/>
-      <c r="AX1" s="154"/>
-      <c r="AY1" s="154"/>
-      <c r="AZ1" s="154"/>
-      <c r="BA1" s="154"/>
-      <c r="BB1" s="154"/>
-      <c r="BC1" s="154"/>
-      <c r="BD1" s="154"/>
-      <c r="BE1" s="154"/>
-      <c r="BF1" s="154"/>
-      <c r="BG1" s="154"/>
-      <c r="BH1" s="155"/>
-      <c r="BI1" s="153" t="s">
+      <c r="AI1" s="150"/>
+      <c r="AJ1" s="150"/>
+      <c r="AK1" s="150"/>
+      <c r="AL1" s="150"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="150"/>
+      <c r="AO1" s="150"/>
+      <c r="AP1" s="150"/>
+      <c r="AQ1" s="150"/>
+      <c r="AR1" s="150"/>
+      <c r="AS1" s="150"/>
+      <c r="AT1" s="150"/>
+      <c r="AU1" s="150"/>
+      <c r="AV1" s="150"/>
+      <c r="AW1" s="150"/>
+      <c r="AX1" s="150"/>
+      <c r="AY1" s="150"/>
+      <c r="AZ1" s="150"/>
+      <c r="BA1" s="150"/>
+      <c r="BB1" s="150"/>
+      <c r="BC1" s="150"/>
+      <c r="BD1" s="150"/>
+      <c r="BE1" s="150"/>
+      <c r="BF1" s="150"/>
+      <c r="BG1" s="150"/>
+      <c r="BH1" s="151"/>
+      <c r="BI1" s="149" t="s">
         <v>163</v>
       </c>
-      <c r="BJ1" s="154"/>
-      <c r="BK1" s="154"/>
-      <c r="BL1" s="154"/>
-      <c r="BM1" s="154"/>
-      <c r="BN1" s="154"/>
-      <c r="BO1" s="154"/>
-      <c r="BP1" s="154"/>
-      <c r="BQ1" s="154"/>
-      <c r="BR1" s="154"/>
-      <c r="BS1" s="154"/>
-      <c r="BT1" s="154"/>
-      <c r="BU1" s="154"/>
-      <c r="BV1" s="154"/>
-      <c r="BW1" s="154"/>
-      <c r="BX1" s="154"/>
-      <c r="BY1" s="154"/>
-      <c r="BZ1" s="154"/>
-      <c r="CA1" s="154"/>
-      <c r="CB1" s="154"/>
-      <c r="CC1" s="154"/>
-      <c r="CD1" s="154"/>
-      <c r="CE1" s="154"/>
-      <c r="CF1" s="154"/>
-      <c r="CG1" s="154"/>
-      <c r="CH1" s="154"/>
-      <c r="CI1" s="155"/>
-      <c r="CJ1" s="153" t="s">
+      <c r="BJ1" s="150"/>
+      <c r="BK1" s="150"/>
+      <c r="BL1" s="150"/>
+      <c r="BM1" s="150"/>
+      <c r="BN1" s="150"/>
+      <c r="BO1" s="150"/>
+      <c r="BP1" s="150"/>
+      <c r="BQ1" s="150"/>
+      <c r="BR1" s="150"/>
+      <c r="BS1" s="150"/>
+      <c r="BT1" s="150"/>
+      <c r="BU1" s="150"/>
+      <c r="BV1" s="150"/>
+      <c r="BW1" s="150"/>
+      <c r="BX1" s="150"/>
+      <c r="BY1" s="150"/>
+      <c r="BZ1" s="150"/>
+      <c r="CA1" s="150"/>
+      <c r="CB1" s="150"/>
+      <c r="CC1" s="150"/>
+      <c r="CD1" s="150"/>
+      <c r="CE1" s="150"/>
+      <c r="CF1" s="150"/>
+      <c r="CG1" s="150"/>
+      <c r="CH1" s="150"/>
+      <c r="CI1" s="151"/>
+      <c r="CJ1" s="149" t="s">
         <v>164</v>
       </c>
-      <c r="CK1" s="154"/>
-      <c r="CL1" s="154"/>
-      <c r="CM1" s="154"/>
-      <c r="CN1" s="154"/>
-      <c r="CO1" s="154"/>
-      <c r="CP1" s="154"/>
-      <c r="CQ1" s="154"/>
-      <c r="CR1" s="154"/>
-      <c r="CS1" s="154"/>
-      <c r="CT1" s="154"/>
-      <c r="CU1" s="154"/>
-      <c r="CV1" s="154"/>
-      <c r="CW1" s="154"/>
-      <c r="CX1" s="154"/>
-      <c r="CY1" s="154"/>
-      <c r="CZ1" s="154"/>
-      <c r="DA1" s="154"/>
-      <c r="DB1" s="154"/>
-      <c r="DC1" s="154"/>
-      <c r="DD1" s="154"/>
-      <c r="DE1" s="154"/>
-      <c r="DF1" s="154"/>
-      <c r="DG1" s="154"/>
-      <c r="DH1" s="154"/>
-      <c r="DI1" s="154"/>
-      <c r="DJ1" s="155"/>
-      <c r="DK1" s="153" t="s">
+      <c r="CK1" s="150"/>
+      <c r="CL1" s="150"/>
+      <c r="CM1" s="150"/>
+      <c r="CN1" s="150"/>
+      <c r="CO1" s="150"/>
+      <c r="CP1" s="150"/>
+      <c r="CQ1" s="150"/>
+      <c r="CR1" s="150"/>
+      <c r="CS1" s="150"/>
+      <c r="CT1" s="150"/>
+      <c r="CU1" s="150"/>
+      <c r="CV1" s="150"/>
+      <c r="CW1" s="150"/>
+      <c r="CX1" s="150"/>
+      <c r="CY1" s="150"/>
+      <c r="CZ1" s="150"/>
+      <c r="DA1" s="150"/>
+      <c r="DB1" s="150"/>
+      <c r="DC1" s="150"/>
+      <c r="DD1" s="150"/>
+      <c r="DE1" s="150"/>
+      <c r="DF1" s="150"/>
+      <c r="DG1" s="150"/>
+      <c r="DH1" s="150"/>
+      <c r="DI1" s="150"/>
+      <c r="DJ1" s="151"/>
+      <c r="DK1" s="149" t="s">
         <v>165</v>
       </c>
-      <c r="DL1" s="154"/>
-      <c r="DM1" s="154"/>
-      <c r="DN1" s="154"/>
-      <c r="DO1" s="154"/>
-      <c r="DP1" s="154"/>
-      <c r="DQ1" s="154"/>
-      <c r="DR1" s="154"/>
-      <c r="DS1" s="154"/>
-      <c r="DT1" s="154"/>
-      <c r="DU1" s="154"/>
-      <c r="DV1" s="154"/>
-      <c r="DW1" s="154"/>
-      <c r="DX1" s="154"/>
-      <c r="DY1" s="154"/>
-      <c r="DZ1" s="154"/>
-      <c r="EA1" s="154"/>
-      <c r="EB1" s="154"/>
-      <c r="EC1" s="154"/>
-      <c r="ED1" s="154"/>
-      <c r="EE1" s="154"/>
-      <c r="EF1" s="154"/>
-      <c r="EG1" s="154"/>
-      <c r="EH1" s="154"/>
-      <c r="EI1" s="154"/>
-      <c r="EJ1" s="154"/>
-      <c r="EK1" s="155"/>
+      <c r="DL1" s="150"/>
+      <c r="DM1" s="150"/>
+      <c r="DN1" s="150"/>
+      <c r="DO1" s="150"/>
+      <c r="DP1" s="150"/>
+      <c r="DQ1" s="150"/>
+      <c r="DR1" s="150"/>
+      <c r="DS1" s="150"/>
+      <c r="DT1" s="150"/>
+      <c r="DU1" s="150"/>
+      <c r="DV1" s="150"/>
+      <c r="DW1" s="150"/>
+      <c r="DX1" s="150"/>
+      <c r="DY1" s="150"/>
+      <c r="DZ1" s="150"/>
+      <c r="EA1" s="150"/>
+      <c r="EB1" s="150"/>
+      <c r="EC1" s="150"/>
+      <c r="ED1" s="150"/>
+      <c r="EE1" s="150"/>
+      <c r="EF1" s="150"/>
+      <c r="EG1" s="150"/>
+      <c r="EH1" s="150"/>
+      <c r="EI1" s="150"/>
+      <c r="EJ1" s="150"/>
+      <c r="EK1" s="151"/>
     </row>
     <row r="2" spans="1:141" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="158" t="s">
+      <c r="E2" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="152"/>
-      <c r="G2" s="158" t="s">
+      <c r="F2" s="156"/>
+      <c r="G2" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="150"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="149" t="s">
+      <c r="H2" s="153"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="150"/>
-      <c r="L2" s="150"/>
-      <c r="M2" s="150"/>
-      <c r="N2" s="150"/>
-      <c r="O2" s="150"/>
-      <c r="P2" s="150"/>
-      <c r="Q2" s="150"/>
-      <c r="R2" s="150"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="150"/>
-      <c r="U2" s="151"/>
-      <c r="V2" s="149" t="s">
+      <c r="K2" s="153"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="153"/>
+      <c r="P2" s="153"/>
+      <c r="Q2" s="153"/>
+      <c r="R2" s="153"/>
+      <c r="S2" s="153"/>
+      <c r="T2" s="153"/>
+      <c r="U2" s="154"/>
+      <c r="V2" s="155" t="s">
         <v>51</v>
       </c>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
-      <c r="Z2" s="150"/>
-      <c r="AA2" s="150"/>
-      <c r="AB2" s="150"/>
-      <c r="AC2" s="150"/>
-      <c r="AD2" s="150"/>
-      <c r="AE2" s="150"/>
-      <c r="AF2" s="150"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="158" t="s">
+      <c r="W2" s="153"/>
+      <c r="X2" s="153"/>
+      <c r="Y2" s="153"/>
+      <c r="Z2" s="153"/>
+      <c r="AA2" s="153"/>
+      <c r="AB2" s="153"/>
+      <c r="AC2" s="153"/>
+      <c r="AD2" s="153"/>
+      <c r="AE2" s="153"/>
+      <c r="AF2" s="153"/>
+      <c r="AG2" s="156"/>
+      <c r="AH2" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="AI2" s="150"/>
-      <c r="AJ2" s="151"/>
-      <c r="AK2" s="149" t="s">
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154"/>
+      <c r="AK2" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="AL2" s="150"/>
-      <c r="AM2" s="150"/>
-      <c r="AN2" s="150"/>
-      <c r="AO2" s="150"/>
-      <c r="AP2" s="150"/>
-      <c r="AQ2" s="150"/>
-      <c r="AR2" s="150"/>
-      <c r="AS2" s="150"/>
-      <c r="AT2" s="150"/>
-      <c r="AU2" s="150"/>
-      <c r="AV2" s="151"/>
-      <c r="AW2" s="149" t="s">
+      <c r="AL2" s="153"/>
+      <c r="AM2" s="153"/>
+      <c r="AN2" s="153"/>
+      <c r="AO2" s="153"/>
+      <c r="AP2" s="153"/>
+      <c r="AQ2" s="153"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="153"/>
+      <c r="AT2" s="153"/>
+      <c r="AU2" s="153"/>
+      <c r="AV2" s="154"/>
+      <c r="AW2" s="155" t="s">
         <v>51</v>
       </c>
-      <c r="AX2" s="150"/>
-      <c r="AY2" s="150"/>
-      <c r="AZ2" s="150"/>
-      <c r="BA2" s="150"/>
-      <c r="BB2" s="150"/>
-      <c r="BC2" s="150"/>
-      <c r="BD2" s="150"/>
-      <c r="BE2" s="150"/>
-      <c r="BF2" s="150"/>
-      <c r="BG2" s="150"/>
-      <c r="BH2" s="152"/>
-      <c r="BI2" s="158" t="s">
+      <c r="AX2" s="153"/>
+      <c r="AY2" s="153"/>
+      <c r="AZ2" s="153"/>
+      <c r="BA2" s="153"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="153"/>
+      <c r="BD2" s="153"/>
+      <c r="BE2" s="153"/>
+      <c r="BF2" s="153"/>
+      <c r="BG2" s="153"/>
+      <c r="BH2" s="156"/>
+      <c r="BI2" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="BJ2" s="150"/>
-      <c r="BK2" s="151"/>
-      <c r="BL2" s="149" t="s">
+      <c r="BJ2" s="153"/>
+      <c r="BK2" s="154"/>
+      <c r="BL2" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="BM2" s="150"/>
-      <c r="BN2" s="150"/>
-      <c r="BO2" s="150"/>
-      <c r="BP2" s="150"/>
-      <c r="BQ2" s="150"/>
-      <c r="BR2" s="150"/>
-      <c r="BS2" s="150"/>
-      <c r="BT2" s="150"/>
-      <c r="BU2" s="150"/>
-      <c r="BV2" s="150"/>
-      <c r="BW2" s="151"/>
-      <c r="BX2" s="149" t="s">
+      <c r="BM2" s="153"/>
+      <c r="BN2" s="153"/>
+      <c r="BO2" s="153"/>
+      <c r="BP2" s="153"/>
+      <c r="BQ2" s="153"/>
+      <c r="BR2" s="153"/>
+      <c r="BS2" s="153"/>
+      <c r="BT2" s="153"/>
+      <c r="BU2" s="153"/>
+      <c r="BV2" s="153"/>
+      <c r="BW2" s="154"/>
+      <c r="BX2" s="155" t="s">
         <v>51</v>
       </c>
-      <c r="BY2" s="150"/>
-      <c r="BZ2" s="150"/>
-      <c r="CA2" s="150"/>
-      <c r="CB2" s="150"/>
-      <c r="CC2" s="150"/>
-      <c r="CD2" s="150"/>
-      <c r="CE2" s="150"/>
-      <c r="CF2" s="150"/>
-      <c r="CG2" s="150"/>
-      <c r="CH2" s="150"/>
-      <c r="CI2" s="152"/>
-      <c r="CJ2" s="158" t="s">
+      <c r="BY2" s="153"/>
+      <c r="BZ2" s="153"/>
+      <c r="CA2" s="153"/>
+      <c r="CB2" s="153"/>
+      <c r="CC2" s="153"/>
+      <c r="CD2" s="153"/>
+      <c r="CE2" s="153"/>
+      <c r="CF2" s="153"/>
+      <c r="CG2" s="153"/>
+      <c r="CH2" s="153"/>
+      <c r="CI2" s="156"/>
+      <c r="CJ2" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="CK2" s="150"/>
-      <c r="CL2" s="151"/>
-      <c r="CM2" s="149" t="s">
+      <c r="CK2" s="153"/>
+      <c r="CL2" s="154"/>
+      <c r="CM2" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="CN2" s="150"/>
-      <c r="CO2" s="150"/>
-      <c r="CP2" s="150"/>
-      <c r="CQ2" s="150"/>
-      <c r="CR2" s="150"/>
-      <c r="CS2" s="150"/>
-      <c r="CT2" s="150"/>
-      <c r="CU2" s="150"/>
-      <c r="CV2" s="150"/>
-      <c r="CW2" s="150"/>
-      <c r="CX2" s="151"/>
-      <c r="CY2" s="149" t="s">
+      <c r="CN2" s="153"/>
+      <c r="CO2" s="153"/>
+      <c r="CP2" s="153"/>
+      <c r="CQ2" s="153"/>
+      <c r="CR2" s="153"/>
+      <c r="CS2" s="153"/>
+      <c r="CT2" s="153"/>
+      <c r="CU2" s="153"/>
+      <c r="CV2" s="153"/>
+      <c r="CW2" s="153"/>
+      <c r="CX2" s="154"/>
+      <c r="CY2" s="155" t="s">
         <v>51</v>
       </c>
-      <c r="CZ2" s="150"/>
-      <c r="DA2" s="150"/>
-      <c r="DB2" s="150"/>
-      <c r="DC2" s="150"/>
-      <c r="DD2" s="150"/>
-      <c r="DE2" s="150"/>
-      <c r="DF2" s="150"/>
-      <c r="DG2" s="150"/>
-      <c r="DH2" s="150"/>
-      <c r="DI2" s="150"/>
-      <c r="DJ2" s="152"/>
-      <c r="DK2" s="158" t="s">
+      <c r="CZ2" s="153"/>
+      <c r="DA2" s="153"/>
+      <c r="DB2" s="153"/>
+      <c r="DC2" s="153"/>
+      <c r="DD2" s="153"/>
+      <c r="DE2" s="153"/>
+      <c r="DF2" s="153"/>
+      <c r="DG2" s="153"/>
+      <c r="DH2" s="153"/>
+      <c r="DI2" s="153"/>
+      <c r="DJ2" s="156"/>
+      <c r="DK2" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="DL2" s="150"/>
-      <c r="DM2" s="151"/>
-      <c r="DN2" s="149" t="s">
+      <c r="DL2" s="153"/>
+      <c r="DM2" s="154"/>
+      <c r="DN2" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="DO2" s="150"/>
-      <c r="DP2" s="150"/>
-      <c r="DQ2" s="150"/>
-      <c r="DR2" s="150"/>
-      <c r="DS2" s="150"/>
-      <c r="DT2" s="150"/>
-      <c r="DU2" s="150"/>
-      <c r="DV2" s="150"/>
-      <c r="DW2" s="150"/>
-      <c r="DX2" s="150"/>
-      <c r="DY2" s="151"/>
-      <c r="DZ2" s="149" t="s">
+      <c r="DO2" s="153"/>
+      <c r="DP2" s="153"/>
+      <c r="DQ2" s="153"/>
+      <c r="DR2" s="153"/>
+      <c r="DS2" s="153"/>
+      <c r="DT2" s="153"/>
+      <c r="DU2" s="153"/>
+      <c r="DV2" s="153"/>
+      <c r="DW2" s="153"/>
+      <c r="DX2" s="153"/>
+      <c r="DY2" s="154"/>
+      <c r="DZ2" s="155" t="s">
         <v>51</v>
       </c>
-      <c r="EA2" s="150"/>
-      <c r="EB2" s="150"/>
-      <c r="EC2" s="150"/>
-      <c r="ED2" s="150"/>
-      <c r="EE2" s="150"/>
-      <c r="EF2" s="150"/>
-      <c r="EG2" s="150"/>
-      <c r="EH2" s="150"/>
-      <c r="EI2" s="150"/>
-      <c r="EJ2" s="150"/>
-      <c r="EK2" s="152"/>
+      <c r="EA2" s="153"/>
+      <c r="EB2" s="153"/>
+      <c r="EC2" s="153"/>
+      <c r="ED2" s="153"/>
+      <c r="EE2" s="153"/>
+      <c r="EF2" s="153"/>
+      <c r="EG2" s="153"/>
+      <c r="EH2" s="153"/>
+      <c r="EI2" s="153"/>
+      <c r="EJ2" s="153"/>
+      <c r="EK2" s="156"/>
     </row>
     <row r="3" spans="1:141" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="90" t="s">
@@ -9226,15 +9206,9 @@
         <f>Neu!$B5</f>
         <v>B63la</v>
       </c>
-      <c r="E32" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="F32" s="17">
-        <v>14</v>
-      </c>
-      <c r="G32" s="17">
-        <v>0.4</v>
-      </c>
+      <c r="E32" s="20"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="43"/>
       <c r="I32" s="17"/>
       <c r="J32" s="19"/>
@@ -9245,12 +9219,8 @@
         <f>Neu!$B5</f>
         <v>B63la</v>
       </c>
-      <c r="P32" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q32" s="19" t="s">
-        <v>161</v>
-      </c>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="19"/>
       <c r="R32" s="43"/>
       <c r="S32" s="19"/>
       <c r="T32" s="43"/>
@@ -10669,6 +10639,20 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="G1:AG1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="AH1:BH1"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AV2"/>
+    <mergeCell ref="AW2:BH2"/>
+    <mergeCell ref="BI1:CI1"/>
+    <mergeCell ref="BI2:BK2"/>
+    <mergeCell ref="BL2:BW2"/>
+    <mergeCell ref="BX2:CI2"/>
     <mergeCell ref="CJ1:DJ1"/>
     <mergeCell ref="CJ2:CL2"/>
     <mergeCell ref="CM2:CX2"/>
@@ -10677,118 +10661,104 @@
     <mergeCell ref="DK2:DM2"/>
     <mergeCell ref="DN2:DY2"/>
     <mergeCell ref="DZ2:EK2"/>
-    <mergeCell ref="AH1:BH1"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AV2"/>
-    <mergeCell ref="AW2:BH2"/>
-    <mergeCell ref="BI1:CI1"/>
-    <mergeCell ref="BI2:BK2"/>
-    <mergeCell ref="BL2:BW2"/>
-    <mergeCell ref="BX2:CI2"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="G1:AG1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A24">
-    <cfRule type="cellIs" dxfId="46" priority="115" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="115" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:D51">
-    <cfRule type="cellIs" dxfId="45" priority="165" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="165" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:EK24">
-    <cfRule type="notContainsBlanks" dxfId="44" priority="5">
+    <cfRule type="notContainsBlanks" dxfId="42" priority="5">
       <formula>LEN(TRIM(E4))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25:AD26">
-    <cfRule type="notContainsBlanks" dxfId="43" priority="18">
+    <cfRule type="notContainsBlanks" dxfId="41" priority="18">
       <formula>LEN(TRIM(G25))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O31:O51">
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z31:Z51">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH25:BE27">
-    <cfRule type="notContainsBlanks" dxfId="40" priority="16">
+    <cfRule type="notContainsBlanks" dxfId="38" priority="16">
       <formula>LEN(TRIM(AH25))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD31:BD51">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI25:BI27">
-    <cfRule type="notContainsBlanks" dxfId="38" priority="91">
+    <cfRule type="notContainsBlanks" dxfId="36" priority="91">
       <formula>LEN(TRIM(BI25))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC26">
-    <cfRule type="notContainsBlanks" dxfId="37" priority="156">
+    <cfRule type="notContainsBlanks" dxfId="35" priority="156">
       <formula>LEN(TRIM(DC26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC25:DG25">
-    <cfRule type="notContainsBlanks" dxfId="36" priority="157">
+    <cfRule type="notContainsBlanks" dxfId="34" priority="157">
       <formula>LEN(TRIM(DC25))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC27:DG27">
-    <cfRule type="notContainsBlanks" dxfId="35" priority="155">
+    <cfRule type="notContainsBlanks" dxfId="33" priority="155">
       <formula>LEN(TRIM(DC27))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DJ25:DJ27">
-    <cfRule type="notContainsBlanks" dxfId="34" priority="84">
+    <cfRule type="notContainsBlanks" dxfId="32" priority="84">
       <formula>LEN(TRIM(DJ25))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK25:EH29">
-    <cfRule type="notContainsBlanks" dxfId="33" priority="81">
+    <cfRule type="notContainsBlanks" dxfId="31" priority="81">
       <formula>LEN(TRIM(DK25))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FE26">
-    <cfRule type="notContainsBlanks" dxfId="32" priority="52">
+    <cfRule type="notContainsBlanks" dxfId="30" priority="52">
       <formula>LEN(TRIM(FE26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FE27:FI27">
-    <cfRule type="notContainsBlanks" dxfId="30" priority="51">
+    <cfRule type="notContainsBlanks" dxfId="29" priority="51">
       <formula>LEN(TRIM(FE27))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FL26:FL27">
-    <cfRule type="notContainsBlanks" dxfId="29" priority="44">
+    <cfRule type="notContainsBlanks" dxfId="28" priority="44">
       <formula>LEN(TRIM(FL26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GL26:GL27">
-    <cfRule type="notContainsBlanks" dxfId="28" priority="75">
+    <cfRule type="notContainsBlanks" dxfId="27" priority="75">
       <formula>LEN(TRIM(GL26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HM26:HM27">
-    <cfRule type="notContainsBlanks" dxfId="27" priority="37">
+    <cfRule type="notContainsBlanks" dxfId="26" priority="37">
       <formula>LEN(TRIM(HM26))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HO29:HO31">
-    <cfRule type="notContainsBlanks" dxfId="26" priority="129">
+    <cfRule type="notContainsBlanks" dxfId="25" priority="129">
       <formula>LEN(TRIM(HO29))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10850,14 +10820,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="F1" s="160" t="s">
+      <c r="F1" s="159" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
       <c r="L1" s="55" t="s">
         <v>46</v>
       </c>
@@ -11050,41 +11020,41 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="156" t="s">
+      <c r="B7" s="157" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="162" t="s">
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="159"/>
-      <c r="K7" s="157"/>
-      <c r="L7" s="156" t="s">
+      <c r="H7" s="162"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="162"/>
+      <c r="K7" s="158"/>
+      <c r="L7" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="159"/>
-      <c r="N7" s="159"/>
-      <c r="O7" s="159"/>
-      <c r="P7" s="157"/>
-      <c r="Q7" s="156" t="s">
+      <c r="M7" s="162"/>
+      <c r="N7" s="162"/>
+      <c r="O7" s="162"/>
+      <c r="P7" s="158"/>
+      <c r="Q7" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="159"/>
-      <c r="S7" s="159"/>
-      <c r="T7" s="159"/>
-      <c r="U7" s="157"/>
-      <c r="V7" s="156" t="s">
+      <c r="R7" s="162"/>
+      <c r="S7" s="162"/>
+      <c r="T7" s="162"/>
+      <c r="U7" s="158"/>
+      <c r="V7" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="W7" s="159"/>
-      <c r="X7" s="159"/>
-      <c r="Y7" s="159"/>
-      <c r="Z7" s="157"/>
+      <c r="W7" s="162"/>
+      <c r="X7" s="162"/>
+      <c r="Y7" s="162"/>
+      <c r="Z7" s="158"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
@@ -11737,46 +11707,46 @@
       <c r="Z23" s="45"/>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A25" s="160" t="s">
+      <c r="A25" s="159" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="160"/>
-      <c r="C25" s="160"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="160"/>
-      <c r="H25" s="160"/>
-      <c r="I25" s="160"/>
-      <c r="J25" s="160"/>
-      <c r="L25" s="160" t="s">
+      <c r="B25" s="159"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="159"/>
+      <c r="J25" s="159"/>
+      <c r="L25" s="159" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="160"/>
+      <c r="M25" s="159"/>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="B26" s="149" t="s">
+      <c r="B26" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="150"/>
-      <c r="D26" s="150"/>
-      <c r="E26" s="151"/>
-      <c r="G26" s="149" t="s">
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="154"/>
+      <c r="G26" s="155" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="150"/>
-      <c r="I26" s="150"/>
-      <c r="J26" s="151"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="153"/>
+      <c r="J26" s="154"/>
       <c r="L26" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="M26" s="163" t="s">
+      <c r="M26" s="160" t="s">
         <v>66</v>
       </c>
-      <c r="N26" s="164"/>
-      <c r="O26" s="164"/>
-      <c r="P26" s="164"/>
-      <c r="Q26" s="164"/>
+      <c r="N26" s="161"/>
+      <c r="O26" s="161"/>
+      <c r="P26" s="161"/>
+      <c r="Q26" s="161"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B27" s="16" t="s">
@@ -11804,11 +11774,11 @@
         <v>67</v>
       </c>
       <c r="L27" s="43"/>
-      <c r="M27" s="163"/>
-      <c r="N27" s="164"/>
-      <c r="O27" s="164"/>
-      <c r="P27" s="164"/>
-      <c r="Q27" s="164"/>
+      <c r="M27" s="160"/>
+      <c r="N27" s="161"/>
+      <c r="O27" s="161"/>
+      <c r="P27" s="161"/>
+      <c r="Q27" s="161"/>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
@@ -12478,17 +12448,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="M26:Q27"/>
     <mergeCell ref="V7:Z7"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="L7:P7"/>
     <mergeCell ref="Q7:U7"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="M26:Q27"/>
   </mergeCells>
   <conditionalFormatting sqref="C3">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="notEqual">
@@ -12552,14 +12522,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="F1" s="160" t="s">
+      <c r="F1" s="159" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
       <c r="L1" s="55" t="s">
         <v>46</v>
       </c>
@@ -12752,41 +12722,41 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="156" t="s">
+      <c r="B7" s="157" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="162" t="s">
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="159"/>
-      <c r="K7" s="157"/>
-      <c r="L7" s="156" t="s">
+      <c r="H7" s="162"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="162"/>
+      <c r="K7" s="158"/>
+      <c r="L7" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="159"/>
-      <c r="N7" s="159"/>
-      <c r="O7" s="159"/>
-      <c r="P7" s="157"/>
-      <c r="Q7" s="156" t="s">
+      <c r="M7" s="162"/>
+      <c r="N7" s="162"/>
+      <c r="O7" s="162"/>
+      <c r="P7" s="158"/>
+      <c r="Q7" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="159"/>
-      <c r="S7" s="159"/>
-      <c r="T7" s="159"/>
-      <c r="U7" s="157"/>
-      <c r="V7" s="156" t="s">
+      <c r="R7" s="162"/>
+      <c r="S7" s="162"/>
+      <c r="T7" s="162"/>
+      <c r="U7" s="158"/>
+      <c r="V7" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="W7" s="159"/>
-      <c r="X7" s="159"/>
-      <c r="Y7" s="159"/>
-      <c r="Z7" s="157"/>
+      <c r="W7" s="162"/>
+      <c r="X7" s="162"/>
+      <c r="Y7" s="162"/>
+      <c r="Z7" s="158"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
@@ -13439,46 +13409,46 @@
       <c r="Z23" s="45"/>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A25" s="160" t="s">
+      <c r="A25" s="159" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="160"/>
-      <c r="C25" s="160"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="160"/>
-      <c r="H25" s="160"/>
-      <c r="I25" s="160"/>
-      <c r="J25" s="160"/>
-      <c r="L25" s="160" t="s">
+      <c r="B25" s="159"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="159"/>
+      <c r="J25" s="159"/>
+      <c r="L25" s="159" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="160"/>
+      <c r="M25" s="159"/>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="B26" s="149" t="s">
+      <c r="B26" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="150"/>
-      <c r="D26" s="150"/>
-      <c r="E26" s="151"/>
-      <c r="G26" s="149" t="s">
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="154"/>
+      <c r="G26" s="155" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="150"/>
-      <c r="I26" s="150"/>
-      <c r="J26" s="151"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="153"/>
+      <c r="J26" s="154"/>
       <c r="L26" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="M26" s="163" t="s">
+      <c r="M26" s="160" t="s">
         <v>66</v>
       </c>
-      <c r="N26" s="164"/>
-      <c r="O26" s="164"/>
-      <c r="P26" s="164"/>
-      <c r="Q26" s="164"/>
+      <c r="N26" s="161"/>
+      <c r="O26" s="161"/>
+      <c r="P26" s="161"/>
+      <c r="Q26" s="161"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B27" s="16" t="s">
@@ -13506,24 +13476,24 @@
         <v>67</v>
       </c>
       <c r="L27" s="43"/>
-      <c r="M27" s="163"/>
-      <c r="N27" s="164"/>
-      <c r="O27" s="164"/>
-      <c r="P27" s="164"/>
-      <c r="Q27" s="164"/>
+      <c r="M27" s="160"/>
+      <c r="N27" s="161"/>
+      <c r="O27" s="161"/>
+      <c r="P27" s="161"/>
+      <c r="Q27" s="161"/>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="43" t="s">
         <v>166</v>
       </c>
       <c r="C28" s="17">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D28" s="17">
         <v>60</v>
       </c>
       <c r="E28" s="17">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
@@ -13533,10 +13503,18 @@
       <c r="M28" s="14"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="B29" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="17">
+        <v>60</v>
+      </c>
+      <c r="E29" s="17">
+        <v>20</v>
+      </c>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
@@ -14209,35 +14187,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="169"/>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169" t="s">
+      <c r="A1" s="168"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
-      <c r="T1" s="169"/>
-      <c r="U1" s="169"/>
-      <c r="V1" s="169"/>
-      <c r="W1" s="169"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="168"/>
+      <c r="P1" s="168"/>
+      <c r="Q1" s="168"/>
+      <c r="R1" s="168"/>
+      <c r="S1" s="168"/>
+      <c r="T1" s="168"/>
+      <c r="U1" s="168"/>
+      <c r="V1" s="168"/>
+      <c r="W1" s="168"/>
     </row>
     <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="169"/>
-      <c r="B2" s="169"/>
+      <c r="A2" s="168"/>
+      <c r="B2" s="168"/>
       <c r="C2" s="134" t="str">
         <f>Neu!$B4</f>
         <v>B63ls</v>
@@ -14324,10 +14302,10 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="168" t="str">
+      <c r="B3" s="165" t="str">
         <f>Neu!B4</f>
         <v>B63ls</v>
       </c>
@@ -14365,7 +14343,7 @@
       <c r="AD3" s="69"/>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="170"/>
+      <c r="A4" s="169"/>
       <c r="B4" s="166"/>
       <c r="C4" s="123"/>
       <c r="D4" s="117"/>
@@ -14402,8 +14380,8 @@
       <c r="AD4" s="69"/>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="170"/>
-      <c r="B5" s="165" t="str">
+      <c r="A5" s="169"/>
+      <c r="B5" s="167" t="str">
         <f>Neu!B5</f>
         <v>B63la</v>
       </c>
@@ -14442,7 +14420,7 @@
       <c r="AD5" s="69"/>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="170"/>
+      <c r="A6" s="169"/>
       <c r="B6" s="166"/>
       <c r="C6" s="127"/>
       <c r="D6" s="118"/>
@@ -14479,8 +14457,8 @@
       <c r="AD6" s="69"/>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="170"/>
-      <c r="B7" s="165" t="str">
+      <c r="A7" s="169"/>
+      <c r="B7" s="167" t="str">
         <f>Neu!B6</f>
         <v>B31rs</v>
       </c>
@@ -14517,7 +14495,7 @@
       <c r="AD7" s="69"/>
     </row>
     <row r="8" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="170"/>
+      <c r="A8" s="169"/>
       <c r="B8" s="166"/>
       <c r="C8" s="127"/>
       <c r="D8" s="102"/>
@@ -14552,8 +14530,8 @@
       <c r="AD8" s="69"/>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="170"/>
-      <c r="B9" s="165" t="str">
+      <c r="A9" s="169"/>
+      <c r="B9" s="167" t="str">
         <f>Neu!B7</f>
         <v>B64ls</v>
       </c>
@@ -14590,7 +14568,7 @@
       <c r="AD9" s="69"/>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="170"/>
+      <c r="A10" s="169"/>
       <c r="B10" s="166"/>
       <c r="C10" s="127"/>
       <c r="D10" s="102"/>
@@ -14625,8 +14603,8 @@
       <c r="AD10" s="69"/>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="170"/>
-      <c r="B11" s="165" t="str">
+      <c r="A11" s="169"/>
+      <c r="B11" s="167" t="str">
         <f>Neu!B8</f>
         <v>B64la</v>
       </c>
@@ -14663,7 +14641,7 @@
       <c r="AD11" s="69"/>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="170"/>
+      <c r="A12" s="169"/>
       <c r="B12" s="166"/>
       <c r="C12" s="127"/>
       <c r="D12" s="102"/>
@@ -14698,8 +14676,8 @@
       <c r="AD12" s="69"/>
     </row>
     <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="170"/>
-      <c r="B13" s="165" t="str">
+      <c r="A13" s="169"/>
+      <c r="B13" s="167" t="str">
         <f>Neu!B9</f>
         <v>B63rs</v>
       </c>
@@ -14736,7 +14714,7 @@
       <c r="AD13" s="69"/>
     </row>
     <row r="14" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="170"/>
+      <c r="A14" s="169"/>
       <c r="B14" s="166"/>
       <c r="C14" s="128"/>
       <c r="D14" s="117"/>
@@ -14771,8 +14749,8 @@
       <c r="AD14" s="69"/>
     </row>
     <row r="15" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="170"/>
-      <c r="B15" s="165" t="str">
+      <c r="A15" s="169"/>
+      <c r="B15" s="167" t="str">
         <f>Neu!B10</f>
         <v>B63ra</v>
       </c>
@@ -14811,7 +14789,7 @@
       <c r="AD15" s="69"/>
     </row>
     <row r="16" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="170"/>
+      <c r="A16" s="169"/>
       <c r="B16" s="166"/>
       <c r="C16" s="127"/>
       <c r="D16" s="102"/>
@@ -14846,8 +14824,8 @@
       <c r="AD16" s="69"/>
     </row>
     <row r="17" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="170"/>
-      <c r="B17" s="165" t="str">
+      <c r="A17" s="169"/>
+      <c r="B17" s="167" t="str">
         <f>Neu!B11</f>
         <v>B31ls</v>
       </c>
@@ -14884,7 +14862,7 @@
       <c r="AD17" s="69"/>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="170"/>
+      <c r="A18" s="169"/>
       <c r="B18" s="166"/>
       <c r="C18" s="127"/>
       <c r="D18" s="102"/>
@@ -14919,8 +14897,8 @@
       <c r="AD18" s="69"/>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="170"/>
-      <c r="B19" s="165" t="str">
+      <c r="A19" s="169"/>
+      <c r="B19" s="167" t="str">
         <f>Neu!B12</f>
         <v>B64rs</v>
       </c>
@@ -14957,7 +14935,7 @@
       <c r="AD19" s="69"/>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="170"/>
+      <c r="A20" s="169"/>
       <c r="B20" s="166"/>
       <c r="C20" s="127"/>
       <c r="D20" s="102"/>
@@ -14992,8 +14970,8 @@
       <c r="AD20" s="69"/>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="170"/>
-      <c r="B21" s="165" t="str">
+      <c r="A21" s="169"/>
+      <c r="B21" s="167" t="str">
         <f>Neu!B13</f>
         <v>B64ra</v>
       </c>
@@ -15030,7 +15008,7 @@
       <c r="AD21" s="69"/>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="170"/>
+      <c r="A22" s="169"/>
       <c r="B22" s="166"/>
       <c r="C22" s="127"/>
       <c r="D22" s="102"/>
@@ -15065,8 +15043,8 @@
       <c r="AD22" s="69"/>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="170"/>
-      <c r="B23" s="165">
+      <c r="A23" s="169"/>
+      <c r="B23" s="167">
         <f>Neu!B14</f>
         <v>0</v>
       </c>
@@ -15103,7 +15081,7 @@
       <c r="AD23" s="69"/>
     </row>
     <row r="24" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="170"/>
+      <c r="A24" s="169"/>
       <c r="B24" s="166"/>
       <c r="C24" s="128"/>
       <c r="D24" s="117"/>
@@ -15138,8 +15116,8 @@
       <c r="AD24" s="69"/>
     </row>
     <row r="25" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="170"/>
-      <c r="B25" s="165">
+      <c r="A25" s="169"/>
+      <c r="B25" s="167">
         <f>Neu!B15</f>
         <v>0</v>
       </c>
@@ -15176,7 +15154,7 @@
       <c r="AD25" s="69"/>
     </row>
     <row r="26" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="170"/>
+      <c r="A26" s="169"/>
       <c r="B26" s="166"/>
       <c r="C26" s="127"/>
       <c r="D26" s="102"/>
@@ -15211,8 +15189,8 @@
       <c r="AD26" s="69"/>
     </row>
     <row r="27" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="170"/>
-      <c r="B27" s="165">
+      <c r="A27" s="169"/>
+      <c r="B27" s="167">
         <f>Neu!B16</f>
         <v>0</v>
       </c>
@@ -15246,7 +15224,7 @@
       <c r="AD27" s="69"/>
     </row>
     <row r="28" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="170"/>
+      <c r="A28" s="169"/>
       <c r="B28" s="166"/>
       <c r="C28" s="127"/>
       <c r="D28" s="102"/>
@@ -15278,8 +15256,8 @@
       <c r="AD28" s="69"/>
     </row>
     <row r="29" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="170"/>
-      <c r="B29" s="165">
+      <c r="A29" s="169"/>
+      <c r="B29" s="167">
         <f>Neu!B17</f>
         <v>0</v>
       </c>
@@ -15313,7 +15291,7 @@
       <c r="AD29" s="69"/>
     </row>
     <row r="30" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="170"/>
+      <c r="A30" s="169"/>
       <c r="B30" s="166"/>
       <c r="C30" s="128"/>
       <c r="D30" s="117"/>
@@ -15345,8 +15323,8 @@
       <c r="AD30" s="69"/>
     </row>
     <row r="31" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="170"/>
-      <c r="B31" s="165">
+      <c r="A31" s="169"/>
+      <c r="B31" s="167">
         <f>Neu!B18</f>
         <v>0</v>
       </c>
@@ -15380,7 +15358,7 @@
       <c r="AD31" s="69"/>
     </row>
     <row r="32" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="170"/>
+      <c r="A32" s="169"/>
       <c r="B32" s="166"/>
       <c r="C32" s="127"/>
       <c r="D32" s="102"/>
@@ -15412,8 +15390,8 @@
       <c r="AD32" s="69"/>
     </row>
     <row r="33" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="170"/>
-      <c r="B33" s="165">
+      <c r="A33" s="169"/>
+      <c r="B33" s="167">
         <f>Neu!B19</f>
         <v>0</v>
       </c>
@@ -15447,7 +15425,7 @@
       <c r="AD33" s="69"/>
     </row>
     <row r="34" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="170"/>
+      <c r="A34" s="169"/>
       <c r="B34" s="166"/>
       <c r="C34" s="127"/>
       <c r="D34" s="102"/>
@@ -15479,8 +15457,8 @@
       <c r="AD34" s="69"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="170"/>
-      <c r="B35" s="165">
+      <c r="A35" s="169"/>
+      <c r="B35" s="167">
         <f>Neu!B20</f>
         <v>0</v>
       </c>
@@ -15514,7 +15492,7 @@
       <c r="AD35" s="69"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="170"/>
+      <c r="A36" s="169"/>
       <c r="B36" s="166"/>
       <c r="C36" s="127"/>
       <c r="D36" s="102"/>
@@ -15546,8 +15524,8 @@
       <c r="AD36" s="69"/>
     </row>
     <row r="37" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="170"/>
-      <c r="B37" s="165">
+      <c r="A37" s="169"/>
+      <c r="B37" s="167">
         <f>Neu!B21</f>
         <v>0</v>
       </c>
@@ -15581,7 +15559,7 @@
       <c r="AD37" s="69"/>
     </row>
     <row r="38" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="170"/>
+      <c r="A38" s="169"/>
       <c r="B38" s="166"/>
       <c r="C38" s="128"/>
       <c r="D38" s="117"/>
@@ -15613,8 +15591,8 @@
       <c r="AD38" s="69"/>
     </row>
     <row r="39" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="170"/>
-      <c r="B39" s="165">
+      <c r="A39" s="169"/>
+      <c r="B39" s="167">
         <f>Neu!B22</f>
         <v>0</v>
       </c>
@@ -15648,7 +15626,7 @@
       <c r="AD39" s="69"/>
     </row>
     <row r="40" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="170"/>
+      <c r="A40" s="169"/>
       <c r="B40" s="166"/>
       <c r="C40" s="127"/>
       <c r="D40" s="102"/>
@@ -15680,8 +15658,8 @@
       <c r="AD40" s="69"/>
     </row>
     <row r="41" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="170"/>
-      <c r="B41" s="165">
+      <c r="A41" s="169"/>
+      <c r="B41" s="167">
         <f>Neu!B23</f>
         <v>0</v>
       </c>
@@ -15715,7 +15693,7 @@
       <c r="AD41" s="69"/>
     </row>
     <row r="42" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="170"/>
+      <c r="A42" s="169"/>
       <c r="B42" s="166"/>
       <c r="C42" s="127"/>
       <c r="D42" s="102"/>
@@ -15747,8 +15725,8 @@
       <c r="AD42" s="69"/>
     </row>
     <row r="43" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="170"/>
-      <c r="B43" s="165">
+      <c r="A43" s="169"/>
+      <c r="B43" s="167">
         <f>Neu!B24</f>
         <v>0</v>
       </c>
@@ -15783,7 +15761,7 @@
     </row>
     <row r="44" spans="1:30" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="113"/>
-      <c r="B44" s="167"/>
+      <c r="B44" s="170"/>
       <c r="C44" s="130"/>
       <c r="D44" s="131"/>
       <c r="E44" s="131"/>
@@ -16775,6 +16753,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A1:B2"/>
@@ -16791,14 +16777,6 @@
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="B3 B5 B7 B9 B11 B13 B15 B17 B19 B21 B23 B25 B27 B29 B31 B33 B35 B37 B39 B41 B43">
     <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
@@ -16852,35 +16830,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="169"/>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169" t="s">
+      <c r="A1" s="168"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
-      <c r="T1" s="169"/>
-      <c r="U1" s="169"/>
-      <c r="V1" s="169"/>
-      <c r="W1" s="169"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="168"/>
+      <c r="P1" s="168"/>
+      <c r="Q1" s="168"/>
+      <c r="R1" s="168"/>
+      <c r="S1" s="168"/>
+      <c r="T1" s="168"/>
+      <c r="U1" s="168"/>
+      <c r="V1" s="168"/>
+      <c r="W1" s="168"/>
     </row>
     <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="169"/>
-      <c r="B2" s="169"/>
+      <c r="A2" s="168"/>
+      <c r="B2" s="168"/>
       <c r="C2" s="134" t="str">
         <f>Neu!$B4</f>
         <v>B63ls</v>
@@ -16967,10 +16945,10 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="168" t="str">
+      <c r="B3" s="165" t="str">
         <f>Neu!B4</f>
         <v>B63ls</v>
       </c>
@@ -17008,7 +16986,7 @@
       <c r="AD3" s="69"/>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="170"/>
+      <c r="A4" s="169"/>
       <c r="B4" s="166"/>
       <c r="C4" s="137"/>
       <c r="D4" s="102"/>
@@ -17045,8 +17023,8 @@
       <c r="AD4" s="69"/>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="170"/>
-      <c r="B5" s="165" t="str">
+      <c r="A5" s="169"/>
+      <c r="B5" s="167" t="str">
         <f>Neu!B5</f>
         <v>B63la</v>
       </c>
@@ -17085,7 +17063,7 @@
       <c r="AD5" s="69"/>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="170"/>
+      <c r="A6" s="169"/>
       <c r="B6" s="166"/>
       <c r="C6" s="135"/>
       <c r="D6" s="118"/>
@@ -17122,8 +17100,8 @@
       <c r="AD6" s="69"/>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="170"/>
-      <c r="B7" s="165" t="str">
+      <c r="A7" s="169"/>
+      <c r="B7" s="167" t="str">
         <f>Neu!B6</f>
         <v>B31rs</v>
       </c>
@@ -17160,7 +17138,7 @@
       <c r="AD7" s="69"/>
     </row>
     <row r="8" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="170"/>
+      <c r="A8" s="169"/>
       <c r="B8" s="166"/>
       <c r="C8" s="135"/>
       <c r="D8" s="102"/>
@@ -17195,8 +17173,8 @@
       <c r="AD8" s="69"/>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="170"/>
-      <c r="B9" s="165" t="str">
+      <c r="A9" s="169"/>
+      <c r="B9" s="167" t="str">
         <f>Neu!B7</f>
         <v>B64ls</v>
       </c>
@@ -17233,7 +17211,7 @@
       <c r="AD9" s="69"/>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="170"/>
+      <c r="A10" s="169"/>
       <c r="B10" s="166"/>
       <c r="C10" s="135"/>
       <c r="D10" s="102"/>
@@ -17268,8 +17246,8 @@
       <c r="AD10" s="69"/>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="170"/>
-      <c r="B11" s="165" t="str">
+      <c r="A11" s="169"/>
+      <c r="B11" s="167" t="str">
         <f>Neu!B8</f>
         <v>B64la</v>
       </c>
@@ -17306,7 +17284,7 @@
       <c r="AD11" s="69"/>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="170"/>
+      <c r="A12" s="169"/>
       <c r="B12" s="166"/>
       <c r="C12" s="136"/>
       <c r="D12" s="117"/>
@@ -17341,8 +17319,8 @@
       <c r="AD12" s="69"/>
     </row>
     <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="170"/>
-      <c r="B13" s="165" t="str">
+      <c r="A13" s="169"/>
+      <c r="B13" s="167" t="str">
         <f>Neu!B9</f>
         <v>B63rs</v>
       </c>
@@ -17379,7 +17357,7 @@
       <c r="AD13" s="69"/>
     </row>
     <row r="14" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="170"/>
+      <c r="A14" s="169"/>
       <c r="B14" s="166"/>
       <c r="C14" s="135"/>
       <c r="D14" s="102"/>
@@ -17414,8 +17392,8 @@
       <c r="AD14" s="69"/>
     </row>
     <row r="15" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="170"/>
-      <c r="B15" s="165" t="str">
+      <c r="A15" s="169"/>
+      <c r="B15" s="167" t="str">
         <f>Neu!B10</f>
         <v>B63ra</v>
       </c>
@@ -17454,7 +17432,7 @@
       <c r="AD15" s="69"/>
     </row>
     <row r="16" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="170"/>
+      <c r="A16" s="169"/>
       <c r="B16" s="166"/>
       <c r="C16" s="135"/>
       <c r="D16" s="102"/>
@@ -17489,8 +17467,8 @@
       <c r="AD16" s="69"/>
     </row>
     <row r="17" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="170"/>
-      <c r="B17" s="165" t="str">
+      <c r="A17" s="169"/>
+      <c r="B17" s="167" t="str">
         <f>Neu!B11</f>
         <v>B31ls</v>
       </c>
@@ -17527,7 +17505,7 @@
       <c r="AD17" s="69"/>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="170"/>
+      <c r="A18" s="169"/>
       <c r="B18" s="166"/>
       <c r="C18" s="135"/>
       <c r="D18" s="102"/>
@@ -17562,8 +17540,8 @@
       <c r="AD18" s="69"/>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="170"/>
-      <c r="B19" s="165" t="str">
+      <c r="A19" s="169"/>
+      <c r="B19" s="167" t="str">
         <f>Neu!B12</f>
         <v>B64rs</v>
       </c>
@@ -17600,7 +17578,7 @@
       <c r="AD19" s="69"/>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="170"/>
+      <c r="A20" s="169"/>
       <c r="B20" s="166"/>
       <c r="C20" s="135"/>
       <c r="D20" s="102"/>
@@ -17635,8 +17613,8 @@
       <c r="AD20" s="69"/>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="170"/>
-      <c r="B21" s="165" t="str">
+      <c r="A21" s="169"/>
+      <c r="B21" s="167" t="str">
         <f>Neu!B13</f>
         <v>B64ra</v>
       </c>
@@ -17673,7 +17651,7 @@
       <c r="AD21" s="69"/>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="170"/>
+      <c r="A22" s="169"/>
       <c r="B22" s="166"/>
       <c r="C22" s="135"/>
       <c r="D22" s="102"/>
@@ -17708,8 +17686,8 @@
       <c r="AD22" s="69"/>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="170"/>
-      <c r="B23" s="165">
+      <c r="A23" s="169"/>
+      <c r="B23" s="167">
         <f>Neu!B14</f>
         <v>0</v>
       </c>
@@ -17746,7 +17724,7 @@
       <c r="AD23" s="69"/>
     </row>
     <row r="24" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="170"/>
+      <c r="A24" s="169"/>
       <c r="B24" s="166"/>
       <c r="C24" s="136"/>
       <c r="D24" s="117"/>
@@ -17781,8 +17759,8 @@
       <c r="AD24" s="69"/>
     </row>
     <row r="25" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="170"/>
-      <c r="B25" s="165">
+      <c r="A25" s="169"/>
+      <c r="B25" s="167">
         <f>Neu!B15</f>
         <v>0</v>
       </c>
@@ -17819,7 +17797,7 @@
       <c r="AD25" s="69"/>
     </row>
     <row r="26" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="170"/>
+      <c r="A26" s="169"/>
       <c r="B26" s="166"/>
       <c r="C26" s="135"/>
       <c r="D26" s="102"/>
@@ -17854,8 +17832,8 @@
       <c r="AD26" s="69"/>
     </row>
     <row r="27" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="170"/>
-      <c r="B27" s="165">
+      <c r="A27" s="169"/>
+      <c r="B27" s="167">
         <f>Neu!B16</f>
         <v>0</v>
       </c>
@@ -17892,7 +17870,7 @@
       <c r="AD27" s="69"/>
     </row>
     <row r="28" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="170"/>
+      <c r="A28" s="169"/>
       <c r="B28" s="166"/>
       <c r="C28" s="135"/>
       <c r="D28" s="102"/>
@@ -17927,8 +17905,8 @@
       <c r="AD28" s="69"/>
     </row>
     <row r="29" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="170"/>
-      <c r="B29" s="165">
+      <c r="A29" s="169"/>
+      <c r="B29" s="167">
         <f>Neu!B17</f>
         <v>0</v>
       </c>
@@ -17965,7 +17943,7 @@
       <c r="AD29" s="69"/>
     </row>
     <row r="30" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="170"/>
+      <c r="A30" s="169"/>
       <c r="B30" s="166"/>
       <c r="C30" s="135"/>
       <c r="D30" s="102"/>
@@ -18000,8 +17978,8 @@
       <c r="AD30" s="69"/>
     </row>
     <row r="31" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="170"/>
-      <c r="B31" s="165">
+      <c r="A31" s="169"/>
+      <c r="B31" s="167">
         <f>Neu!B18</f>
         <v>0</v>
       </c>
@@ -18038,7 +18016,7 @@
       <c r="AD31" s="69"/>
     </row>
     <row r="32" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="170"/>
+      <c r="A32" s="169"/>
       <c r="B32" s="166"/>
       <c r="C32" s="135"/>
       <c r="D32" s="102"/>
@@ -18073,8 +18051,8 @@
       <c r="AD32" s="69"/>
     </row>
     <row r="33" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="170"/>
-      <c r="B33" s="165">
+      <c r="A33" s="169"/>
+      <c r="B33" s="167">
         <f>Neu!B19</f>
         <v>0</v>
       </c>
@@ -18108,7 +18086,7 @@
       <c r="AD33" s="69"/>
     </row>
     <row r="34" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="170"/>
+      <c r="A34" s="169"/>
       <c r="B34" s="166"/>
       <c r="C34" s="135"/>
       <c r="D34" s="102"/>
@@ -18140,8 +18118,8 @@
       <c r="AD34" s="69"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="170"/>
-      <c r="B35" s="165">
+      <c r="A35" s="169"/>
+      <c r="B35" s="167">
         <f>Neu!B20</f>
         <v>0</v>
       </c>
@@ -18175,7 +18153,7 @@
       <c r="AD35" s="69"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="170"/>
+      <c r="A36" s="169"/>
       <c r="B36" s="166"/>
       <c r="C36" s="136"/>
       <c r="D36" s="117"/>
@@ -18207,8 +18185,8 @@
       <c r="AD36" s="69"/>
     </row>
     <row r="37" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="170"/>
-      <c r="B37" s="165">
+      <c r="A37" s="169"/>
+      <c r="B37" s="167">
         <f>Neu!B21</f>
         <v>0</v>
       </c>
@@ -18242,7 +18220,7 @@
       <c r="AD37" s="69"/>
     </row>
     <row r="38" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="170"/>
+      <c r="A38" s="169"/>
       <c r="B38" s="166"/>
       <c r="C38" s="135"/>
       <c r="D38" s="102"/>
@@ -18274,8 +18252,8 @@
       <c r="AD38" s="69"/>
     </row>
     <row r="39" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="170"/>
-      <c r="B39" s="165">
+      <c r="A39" s="169"/>
+      <c r="B39" s="167">
         <f>Neu!B22</f>
         <v>0</v>
       </c>
@@ -18309,7 +18287,7 @@
       <c r="AD39" s="69"/>
     </row>
     <row r="40" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="170"/>
+      <c r="A40" s="169"/>
       <c r="B40" s="166"/>
       <c r="C40" s="135"/>
       <c r="D40" s="102"/>
@@ -18341,8 +18319,8 @@
       <c r="AD40" s="69"/>
     </row>
     <row r="41" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="170"/>
-      <c r="B41" s="165">
+      <c r="A41" s="169"/>
+      <c r="B41" s="167">
         <f>Neu!B23</f>
         <v>0</v>
       </c>
@@ -18376,7 +18354,7 @@
       <c r="AD41" s="69"/>
     </row>
     <row r="42" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="170"/>
+      <c r="A42" s="169"/>
       <c r="B42" s="166"/>
       <c r="C42" s="135"/>
       <c r="D42" s="102"/>
@@ -18408,8 +18386,8 @@
       <c r="AD42" s="69"/>
     </row>
     <row r="43" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="170"/>
-      <c r="B43" s="165">
+      <c r="A43" s="169"/>
+      <c r="B43" s="167">
         <f>Neu!B24</f>
         <v>0</v>
       </c>
@@ -18444,7 +18422,7 @@
     </row>
     <row r="44" spans="1:30" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="113"/>
-      <c r="B44" s="167"/>
+      <c r="B44" s="170"/>
       <c r="C44" s="139"/>
       <c r="D44" s="131"/>
       <c r="E44" s="131"/>
@@ -19436,6 +19414,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A3:A43"/>
@@ -19452,14 +19438,6 @@
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
   </mergeCells>
   <conditionalFormatting sqref="B3 B5 B7 B9 B11 B13 B15 B17 B19 B21 B23 B25 B27 B29 B31 B33 B35 B37 B39 B41 B43">
     <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
@@ -19537,8 +19515,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="169"/>
-      <c r="B1" s="169"/>
+      <c r="A1" s="168"/>
+      <c r="B1" s="168"/>
       <c r="C1" s="174" t="s">
         <v>4</v>
       </c>
@@ -19582,8 +19560,8 @@
       <c r="AJ1" s="171"/>
     </row>
     <row r="2" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="169"/>
-      <c r="B2" s="169"/>
+      <c r="A2" s="168"/>
+      <c r="B2" s="168"/>
       <c r="C2" s="134" t="str">
         <f>Neu!$B4</f>
         <v>B63ls</v>
@@ -19700,10 +19678,10 @@
       </c>
     </row>
     <row r="3" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="168" t="str">
+      <c r="B3" s="165" t="str">
         <f>Neu!B4</f>
         <v>B63ls</v>
       </c>
@@ -19758,7 +19736,7 @@
       <c r="AK3" s="70"/>
     </row>
     <row r="4" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="170"/>
+      <c r="A4" s="169"/>
       <c r="B4" s="166"/>
       <c r="C4" s="123"/>
       <c r="D4" s="117"/>
@@ -19819,8 +19797,8 @@
       <c r="AK4" s="70"/>
     </row>
     <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="170"/>
-      <c r="B5" s="165" t="str">
+      <c r="A5" s="169"/>
+      <c r="B5" s="167" t="str">
         <f>Neu!B5</f>
         <v>B63la</v>
       </c>
@@ -19857,7 +19835,7 @@
       </c>
     </row>
     <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="170"/>
+      <c r="A6" s="169"/>
       <c r="B6" s="166"/>
       <c r="C6" s="127"/>
       <c r="D6" s="118"/>
@@ -19892,8 +19870,8 @@
       </c>
     </row>
     <row r="7" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="170"/>
-      <c r="B7" s="165" t="str">
+      <c r="A7" s="169"/>
+      <c r="B7" s="167" t="str">
         <f>Neu!B6</f>
         <v>B31rs</v>
       </c>
@@ -19928,7 +19906,7 @@
       </c>
     </row>
     <row r="8" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="170"/>
+      <c r="A8" s="169"/>
       <c r="B8" s="166"/>
       <c r="C8" s="127"/>
       <c r="D8" s="102"/>
@@ -19961,8 +19939,8 @@
       </c>
     </row>
     <row r="9" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="170"/>
-      <c r="B9" s="165" t="str">
+      <c r="A9" s="169"/>
+      <c r="B9" s="167" t="str">
         <f>Neu!B7</f>
         <v>B64ls</v>
       </c>
@@ -20000,7 +19978,7 @@
       </c>
     </row>
     <row r="10" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="170"/>
+      <c r="A10" s="169"/>
       <c r="B10" s="166"/>
       <c r="C10" s="127"/>
       <c r="D10" s="102"/>
@@ -20034,8 +20012,8 @@
       <c r="AL10" s="70"/>
     </row>
     <row r="11" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="170"/>
-      <c r="B11" s="165" t="str">
+      <c r="A11" s="169"/>
+      <c r="B11" s="167" t="str">
         <f>Neu!B8</f>
         <v>B64la</v>
       </c>
@@ -20070,7 +20048,7 @@
       </c>
     </row>
     <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="170"/>
+      <c r="A12" s="169"/>
       <c r="B12" s="166"/>
       <c r="C12" s="127"/>
       <c r="D12" s="102"/>
@@ -20103,8 +20081,8 @@
       </c>
     </row>
     <row r="13" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="170"/>
-      <c r="B13" s="165" t="str">
+      <c r="A13" s="169"/>
+      <c r="B13" s="167" t="str">
         <f>Neu!B9</f>
         <v>B63rs</v>
       </c>
@@ -20142,7 +20120,7 @@
       </c>
     </row>
     <row r="14" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="170"/>
+      <c r="A14" s="169"/>
       <c r="B14" s="166"/>
       <c r="C14" s="127"/>
       <c r="D14" s="102"/>
@@ -20179,8 +20157,8 @@
       </c>
     </row>
     <row r="15" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="170"/>
-      <c r="B15" s="165" t="str">
+      <c r="A15" s="169"/>
+      <c r="B15" s="167" t="str">
         <f>Neu!B10</f>
         <v>B63ra</v>
       </c>
@@ -20217,7 +20195,7 @@
       </c>
     </row>
     <row r="16" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="170"/>
+      <c r="A16" s="169"/>
       <c r="B16" s="166"/>
       <c r="C16" s="128"/>
       <c r="D16" s="117"/>
@@ -20250,8 +20228,8 @@
       </c>
     </row>
     <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="170"/>
-      <c r="B17" s="165" t="str">
+      <c r="A17" s="169"/>
+      <c r="B17" s="167" t="str">
         <f>Neu!B11</f>
         <v>B31ls</v>
       </c>
@@ -20286,7 +20264,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="170"/>
+      <c r="A18" s="169"/>
       <c r="B18" s="166"/>
       <c r="C18" s="127"/>
       <c r="D18" s="102"/>
@@ -20319,8 +20297,8 @@
       </c>
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="170"/>
-      <c r="B19" s="165" t="str">
+      <c r="A19" s="169"/>
+      <c r="B19" s="167" t="str">
         <f>Neu!B12</f>
         <v>B64rs</v>
       </c>
@@ -20355,7 +20333,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="170"/>
+      <c r="A20" s="169"/>
       <c r="B20" s="166"/>
       <c r="C20" s="127"/>
       <c r="D20" s="102"/>
@@ -20388,8 +20366,8 @@
       </c>
     </row>
     <row r="21" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="170"/>
-      <c r="B21" s="165" t="str">
+      <c r="A21" s="169"/>
+      <c r="B21" s="167" t="str">
         <f>Neu!B13</f>
         <v>B64ra</v>
       </c>
@@ -20424,7 +20402,7 @@
       </c>
     </row>
     <row r="22" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="170"/>
+      <c r="A22" s="169"/>
       <c r="B22" s="166"/>
       <c r="C22" s="127"/>
       <c r="D22" s="102"/>
@@ -20457,8 +20435,8 @@
       </c>
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="170"/>
-      <c r="B23" s="165">
+      <c r="A23" s="169"/>
+      <c r="B23" s="167">
         <f>Neu!B14</f>
         <v>0</v>
       </c>
@@ -20493,7 +20471,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="170"/>
+      <c r="A24" s="169"/>
       <c r="B24" s="166"/>
       <c r="C24" s="128"/>
       <c r="D24" s="117"/>
@@ -20526,8 +20504,8 @@
       </c>
     </row>
     <row r="25" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="170"/>
-      <c r="B25" s="165">
+      <c r="A25" s="169"/>
+      <c r="B25" s="167">
         <f>Neu!B15</f>
         <v>0</v>
       </c>
@@ -20562,7 +20540,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="170"/>
+      <c r="A26" s="169"/>
       <c r="B26" s="166"/>
       <c r="C26" s="127"/>
       <c r="D26" s="102"/>
@@ -20595,8 +20573,8 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="170"/>
-      <c r="B27" s="165">
+      <c r="A27" s="169"/>
+      <c r="B27" s="167">
         <f>Neu!B16</f>
         <v>0</v>
       </c>
@@ -20631,7 +20609,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="170"/>
+      <c r="A28" s="169"/>
       <c r="B28" s="166"/>
       <c r="C28" s="127"/>
       <c r="D28" s="102"/>
@@ -20664,8 +20642,8 @@
       </c>
     </row>
     <row r="29" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="170"/>
-      <c r="B29" s="165">
+      <c r="A29" s="169"/>
+      <c r="B29" s="167">
         <f>Neu!B17</f>
         <v>0</v>
       </c>
@@ -20700,7 +20678,7 @@
       </c>
     </row>
     <row r="30" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="170"/>
+      <c r="A30" s="169"/>
       <c r="B30" s="166"/>
       <c r="C30" s="127"/>
       <c r="D30" s="102"/>
@@ -20733,8 +20711,8 @@
       </c>
     </row>
     <row r="31" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="170"/>
-      <c r="B31" s="165">
+      <c r="A31" s="169"/>
+      <c r="B31" s="167">
         <f>Neu!B18</f>
         <v>0</v>
       </c>
@@ -20769,7 +20747,7 @@
       </c>
     </row>
     <row r="32" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="170"/>
+      <c r="A32" s="169"/>
       <c r="B32" s="166"/>
       <c r="C32" s="128"/>
       <c r="D32" s="117"/>
@@ -20802,8 +20780,8 @@
       </c>
     </row>
     <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="170"/>
-      <c r="B33" s="165">
+      <c r="A33" s="169"/>
+      <c r="B33" s="167">
         <f>Neu!B19</f>
         <v>0</v>
       </c>
@@ -20838,7 +20816,7 @@
       </c>
     </row>
     <row r="34" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="170"/>
+      <c r="A34" s="169"/>
       <c r="B34" s="166"/>
       <c r="C34" s="127"/>
       <c r="D34" s="102"/>
@@ -20871,8 +20849,8 @@
       </c>
     </row>
     <row r="35" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="170"/>
-      <c r="B35" s="165">
+      <c r="A35" s="169"/>
+      <c r="B35" s="167">
         <f>Neu!B20</f>
         <v>0</v>
       </c>
@@ -20907,7 +20885,7 @@
       </c>
     </row>
     <row r="36" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="170"/>
+      <c r="A36" s="169"/>
       <c r="B36" s="166"/>
       <c r="C36" s="127"/>
       <c r="D36" s="102"/>
@@ -20940,8 +20918,8 @@
       </c>
     </row>
     <row r="37" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="170"/>
-      <c r="B37" s="165">
+      <c r="A37" s="169"/>
+      <c r="B37" s="167">
         <f>Neu!B21</f>
         <v>0</v>
       </c>
@@ -20976,7 +20954,7 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="170"/>
+      <c r="A38" s="169"/>
       <c r="B38" s="166"/>
       <c r="C38" s="127"/>
       <c r="D38" s="102"/>
@@ -21009,8 +20987,8 @@
       </c>
     </row>
     <row r="39" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="170"/>
-      <c r="B39" s="165">
+      <c r="A39" s="169"/>
+      <c r="B39" s="167">
         <f>Neu!B22</f>
         <v>0</v>
       </c>
@@ -21045,7 +21023,7 @@
       </c>
     </row>
     <row r="40" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="170"/>
+      <c r="A40" s="169"/>
       <c r="B40" s="166"/>
       <c r="C40" s="127"/>
       <c r="D40" s="102"/>
@@ -21078,8 +21056,8 @@
       </c>
     </row>
     <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="170"/>
-      <c r="B41" s="165">
+      <c r="A41" s="169"/>
+      <c r="B41" s="167">
         <f>Neu!B23</f>
         <v>0</v>
       </c>
@@ -21114,7 +21092,7 @@
       </c>
     </row>
     <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="170"/>
+      <c r="A42" s="169"/>
       <c r="B42" s="166"/>
       <c r="C42" s="127"/>
       <c r="D42" s="102"/>
@@ -21147,8 +21125,8 @@
       </c>
     </row>
     <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="170"/>
-      <c r="B43" s="165">
+      <c r="A43" s="169"/>
+      <c r="B43" s="167">
         <f>Neu!B24</f>
         <v>0</v>
       </c>
@@ -21184,7 +21162,7 @@
     </row>
     <row r="44" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="113"/>
-      <c r="B44" s="167"/>
+      <c r="B44" s="170"/>
       <c r="C44" s="130"/>
       <c r="D44" s="131"/>
       <c r="E44" s="131"/>
@@ -22330,11 +22308,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C1:W1"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="A1:B2"/>
@@ -22351,12 +22330,11 @@
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C1:W1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3 B5 B7 B9 B11 B13 B15 B17 B19 B21 B23 B25 B27 B29 B31 B33 B35 B37 B39 B41 B43">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
